--- a/members.xlsx
+++ b/members.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Desktop\AWO_Celebrate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Desktop\general\AWO_Celebrate\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -520,112 +520,112 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>921761067</v>
+        <v>910045632</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1">
-        <v>912861288</v>
+        <v>921761067</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1">
-        <v>922956646</v>
+        <v>912861288</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1">
-        <v>913235855</v>
+        <v>922956646</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1">
-        <v>948594041</v>
+        <v>913235855</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C12" s="1">
-        <v>911853155</v>
+        <v>948594041</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C13" s="1">
-        <v>985816078</v>
+        <v>911853155</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C14" s="1">
-        <v>913942964</v>
+        <v>985816078</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C15" s="1">
-        <v>925382373</v>
+        <v>913942964</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C16" s="1">
-        <v>910045632</v>
+        <v>925382373</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">

--- a/members.xlsx
+++ b/members.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
   <si>
     <t>Addunnaa</t>
   </si>
@@ -117,12 +117,6 @@
   </si>
   <si>
     <t>Lalisee</t>
-  </si>
-  <si>
-    <t>Dabaree</t>
-  </si>
-  <si>
-    <t>Fayyeeraa</t>
   </si>
 </sst>
 </file>
@@ -444,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -639,17 +633,6 @@
         <v>954846351</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="1">
-        <v>912214364</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
